--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,14 +722,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45163.6087794206</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -775,15 +771,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="18" customHeight="1" s="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -946,10 +933,6 @@
         <v>760</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -960,19 +943,19 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,7 +722,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,7 +722,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45239</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -942,20 +942,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,7 +722,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -942,20 +942,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,7 +722,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,7 +722,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,10 +722,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45266</v>
+        <v>45163.6087794206</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -771,6 +775,15 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1" s="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -933,6 +946,10 @@
         <v>760</v>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -943,19 +960,19 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
+++ b/LISTAS/ma/FLEXIBLE GAS DISMAY.xlsx
@@ -722,14 +722,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45163.6087794206</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -775,15 +771,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="18" customHeight="1" s="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
@@ -946,10 +933,6 @@
         <v>760</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -959,20 +942,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
